--- a/r-eco-pilot_users.xlsx
+++ b/r-eco-pilot_users.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Admin" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Teachers" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sages" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Students (ห้อง สทธ.68-11)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="นักศึกษา สทธ.69-11" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Accounts" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ทั้งหมด" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
@@ -138,13 +138,13 @@
   <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -153,25 +153,25 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -633,7 +633,7 @@
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="32" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -724,7 +724,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>ทีม ปวีณา (นักเรียน 01-07)</t>
+          <t>ทีม ปวีณา</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>ทีม กุลิสรา (นักเรียน 08-14)</t>
+          <t>ทีม กุลิสรา</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>ทีม อัญชลี (นักเรียน 15-20)</t>
+          <t>ทีม อัญชลี</t>
         </is>
       </c>
     </row>
@@ -913,16 +913,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -943,7 +943,7 @@
       </c>
       <c r="D1" s="8" t="inlineStr">
         <is>
-          <t>Username</t>
+          <t>Username (รหัสนักศึกษา)</t>
         </is>
       </c>
       <c r="E1" s="8" t="inlineStr">
@@ -958,7 +958,7 @@
       </c>
       <c r="G1" s="8" t="inlineStr">
         <is>
-          <t>ทีม</t>
+          <t>ห้อง</t>
         </is>
       </c>
     </row>
@@ -968,17 +968,17 @@
       </c>
       <c r="B2" s="9" t="inlineStr">
         <is>
-          <t>กฤติยาภรณ์ เพ็ชรดี</t>
+          <t>ศิริญา นาคสมบูรณ์</t>
         </is>
       </c>
       <c r="C2" s="9" t="inlineStr">
         <is>
-          <t>ใบเตย</t>
+          <t>การ์ฟิลด์</t>
         </is>
       </c>
       <c r="D2" s="9" t="inlineStr">
         <is>
-          <t>student01</t>
+          <t>6932040001</t>
         </is>
       </c>
       <c r="E2" s="9" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="G2" s="9" t="inlineStr">
         <is>
-          <t>ทีม ปวีณา</t>
+          <t>สทธ.69-11</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>สุทธิตา แซ่ลิ้ม</t>
+          <t>ธนากร บัวติ๊บ</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>เอิร์น</t>
+          <t>โด่ง</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>student02</t>
+          <t>6932040002</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -1028,7 +1028,7 @@
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>ทีม ปวีณา</t>
+          <t>สทธ.69-11</t>
         </is>
       </c>
     </row>
@@ -1038,13 +1038,17 @@
       </c>
       <c r="B4" s="9" t="inlineStr">
         <is>
-          <t>เพ็ญพิชญา มีสรรเสริญ</t>
-        </is>
-      </c>
-      <c r="C4" s="9" t="inlineStr"/>
+          <t>ดานิโล อโนทัย เดนตี้</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>โตโล่</t>
+        </is>
+      </c>
       <c r="D4" s="9" t="inlineStr">
         <is>
-          <t>student03</t>
+          <t>6932040003</t>
         </is>
       </c>
       <c r="E4" s="9" t="inlineStr">
@@ -1059,7 +1063,7 @@
       </c>
       <c r="G4" s="9" t="inlineStr">
         <is>
-          <t>ทีม ปวีณา</t>
+          <t>สทธ.69-11</t>
         </is>
       </c>
     </row>
@@ -1069,17 +1073,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>ญาณวรรณ ดาบทอง</t>
+          <t>พิชญา ประทุมเพ็ชร</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>ฝ้าย</t>
+          <t>มิว</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>student04</t>
+          <t>6932040006</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -1094,7 +1098,7 @@
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>ทีม ปวีณา</t>
+          <t>สทธ.69-11</t>
         </is>
       </c>
     </row>
@@ -1104,17 +1108,13 @@
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>จุติรัตน์ วังเวง</t>
-        </is>
-      </c>
-      <c r="C6" s="9" t="inlineStr">
-        <is>
-          <t>วีต้า</t>
-        </is>
-      </c>
+          <t>วันสุ นิ่มประเสริฐ</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr"/>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>student05</t>
+          <t>6932040007</t>
         </is>
       </c>
       <c r="E6" s="9" t="inlineStr">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="G6" s="9" t="inlineStr">
         <is>
-          <t>ทีม ปวีณา</t>
+          <t>สทธ.69-11</t>
         </is>
       </c>
     </row>
@@ -1139,17 +1139,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>นิตินัดดา สายศรี</t>
+          <t>วรชิต เขียวหวาน</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>ดาด้า</t>
+          <t>ฟาร์ม</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>student06</t>
+          <t>6932040008</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>ทีม ปวีณา</t>
+          <t>สทธ.69-11</t>
         </is>
       </c>
     </row>
@@ -1174,17 +1174,17 @@
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>ศิริวิมล อ่ำอิ่ม</t>
+          <t>ปวเรศ จำพานิชย์</t>
         </is>
       </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
-          <t>แก้ม</t>
+          <t>คิง</t>
         </is>
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>student07</t>
+          <t>6932040009</t>
         </is>
       </c>
       <c r="E8" s="9" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="G8" s="9" t="inlineStr">
         <is>
-          <t>ทีม ปวีณา</t>
+          <t>สทธ.69-11</t>
         </is>
       </c>
     </row>
@@ -1209,17 +1209,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>อภิชญา เมืองศิริ</t>
+          <t>เสฎฐวุฒิ แสนบุญมี</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>เมจิ</t>
+          <t>เจมส์</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>student08</t>
+          <t>6932040010</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -1234,7 +1234,7 @@
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>ทีม กุลิสรา</t>
+          <t>สทธ.69-11</t>
         </is>
       </c>
     </row>
@@ -1244,17 +1244,17 @@
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>เมธนิยา ยางคำ</t>
+          <t>ปวีณ์นุช บินหะยีอาระซัน</t>
         </is>
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>มายด์</t>
+          <t>อัลนูร</t>
         </is>
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>student09</t>
+          <t>6932040011</t>
         </is>
       </c>
       <c r="E10" s="9" t="inlineStr">
@@ -1269,7 +1269,7 @@
       </c>
       <c r="G10" s="9" t="inlineStr">
         <is>
-          <t>ทีม กุลิสรา</t>
+          <t>สทธ.69-11</t>
         </is>
       </c>
     </row>
@@ -1279,17 +1279,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>ณัฐภัทร กอบสันเทียะ</t>
+          <t>ฟ่ะฮัด ชัยพฤกษ์</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>เป้</t>
+          <t>ฟาฮัด</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>student10</t>
+          <t>6932040012</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -1304,7 +1304,7 @@
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>ทีม กุลิสรา</t>
+          <t>สทธ.69-11</t>
         </is>
       </c>
     </row>
@@ -1314,13 +1314,13 @@
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>พรนภัส ภูฆัง</t>
+          <t>ปฏิวิทย์ แซ่ลิ่ม</t>
         </is>
       </c>
       <c r="C12" s="9" t="inlineStr"/>
       <c r="D12" s="9" t="inlineStr">
         <is>
-          <t>student11</t>
+          <t>6932040013</t>
         </is>
       </c>
       <c r="E12" s="9" t="inlineStr">
@@ -1335,7 +1335,7 @@
       </c>
       <c r="G12" s="9" t="inlineStr">
         <is>
-          <t>ทีม กุลิสรา</t>
+          <t>สทธ.69-11</t>
         </is>
       </c>
     </row>
@@ -1345,17 +1345,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>กุลธิดา บุญเฮง</t>
+          <t>ถิระศักดิ์ ไสยกิจ</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>มาร์ยู</t>
+          <t>โบ๊ท</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>student12</t>
+          <t>6932040015</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>ทีม กุลิสรา</t>
+          <t>สทธ.69-11</t>
         </is>
       </c>
     </row>
@@ -1380,17 +1380,17 @@
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>วัชรวิทย์ ดาราวงศ์</t>
+          <t>กนกวรรณ สุภาพ</t>
         </is>
       </c>
       <c r="C14" s="9" t="inlineStr">
         <is>
-          <t>ไอซ์</t>
+          <t>หยก</t>
         </is>
       </c>
       <c r="D14" s="9" t="inlineStr">
         <is>
-          <t>student13</t>
+          <t>6932040016</t>
         </is>
       </c>
       <c r="E14" s="9" t="inlineStr">
@@ -1405,7 +1405,7 @@
       </c>
       <c r="G14" s="9" t="inlineStr">
         <is>
-          <t>ทีม กุลิสรา</t>
+          <t>สทธ.69-11</t>
         </is>
       </c>
     </row>
@@ -1415,13 +1415,17 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>หทัยกาญ ศิริถาวรเลิศสกุล</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="inlineStr"/>
+          <t>ประวีณ ผลถวิล</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>เหนือ</t>
+        </is>
+      </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>student14</t>
+          <t>6932040017</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -1436,7 +1440,7 @@
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>ทีม กุลิสรา</t>
+          <t>สทธ.69-11</t>
         </is>
       </c>
     </row>
@@ -1446,17 +1450,17 @@
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>วิทวัส หลักเพชร</t>
+          <t>กัญญาวีร์ พิทักษ์ลักษณ์</t>
         </is>
       </c>
       <c r="C16" s="9" t="inlineStr">
         <is>
-          <t>บิ๊ก</t>
+          <t>ฮาบี</t>
         </is>
       </c>
       <c r="D16" s="9" t="inlineStr">
         <is>
-          <t>student15</t>
+          <t>6932040018</t>
         </is>
       </c>
       <c r="E16" s="9" t="inlineStr">
@@ -1471,7 +1475,7 @@
       </c>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>ทีม อัญชลี</t>
+          <t>สทธ.69-11</t>
         </is>
       </c>
     </row>
@@ -1481,17 +1485,13 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>ศิริประภา เสภารัตน์</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>ใบหม่อน</t>
-        </is>
-      </c>
+          <t>เคอหนุ่ม</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr"/>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>student16</t>
+          <t>6932040020</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>ทีม อัญชลี</t>
+          <t>สทธ.69-11</t>
         </is>
       </c>
     </row>
@@ -1516,17 +1516,17 @@
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>วิภาช บรรจงอักษร</t>
+          <t>ทิราภรณ์ ทองเกษมศรี</t>
         </is>
       </c>
       <c r="C18" s="9" t="inlineStr">
         <is>
-          <t>กี้</t>
+          <t>บิว</t>
         </is>
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
-          <t>student17</t>
+          <t>6932040021</t>
         </is>
       </c>
       <c r="E18" s="9" t="inlineStr">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="G18" s="9" t="inlineStr">
         <is>
-          <t>ทีม อัญชลี</t>
+          <t>สทธ.69-11</t>
         </is>
       </c>
     </row>
@@ -1551,17 +1551,17 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>ขจรเกียรติ สุขบัติ</t>
+          <t>ธนัชชา จุ้ยรอด</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>เต</t>
+          <t>ออมสิน</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>student18</t>
+          <t>6932040022</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -1576,7 +1576,7 @@
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>ทีม อัญชลี</t>
+          <t>สทธ.69-11</t>
         </is>
       </c>
     </row>
@@ -1586,17 +1586,17 @@
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>จักรพรรดิ์ อาวาส</t>
+          <t>สุภัสสรา บุญแต่ง</t>
         </is>
       </c>
       <c r="C20" s="9" t="inlineStr">
         <is>
-          <t>ธีร์</t>
+          <t>รถแจ๊ส</t>
         </is>
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>student19</t>
+          <t>6932040023</t>
         </is>
       </c>
       <c r="E20" s="9" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="G20" s="9" t="inlineStr">
         <is>
-          <t>ทีม อัญชลี</t>
+          <t>สทธ.69-11</t>
         </is>
       </c>
     </row>
@@ -1621,17 +1621,17 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>อดิเทพ พลทะสี</t>
+          <t>ธัญกมล เพ็ชรธนดำรง</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>แบงค์</t>
+          <t>เอด้า</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>student20</t>
+          <t>6932040024</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -1646,7 +1646,147 @@
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>ทีม อัญชลี</t>
+          <t>สทธ.69-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="9" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>สุจิรา วงศ์เกิดสุข</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>น้ำปั่น</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="inlineStr">
+        <is>
+          <t>6932040025</t>
+        </is>
+      </c>
+      <c r="E22" s="9" t="inlineStr">
+        <is>
+          <t>student123</t>
+        </is>
+      </c>
+      <c r="F22" s="9" t="inlineStr">
+        <is>
+          <t>student</t>
+        </is>
+      </c>
+      <c r="G22" s="9" t="inlineStr">
+        <is>
+          <t>สทธ.69-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>ตรีรัตน์ ศรีภุมมา</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>นัท</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>6932040026</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>student123</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>student</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>สทธ.69-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="9" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>วัชรวิศว์ เปล่งปลั่ง</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>เฟส</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="inlineStr">
+        <is>
+          <t>6932040027</t>
+        </is>
+      </c>
+      <c r="E24" s="9" t="inlineStr">
+        <is>
+          <t>student123</t>
+        </is>
+      </c>
+      <c r="F24" s="9" t="inlineStr">
+        <is>
+          <t>student</t>
+        </is>
+      </c>
+      <c r="G24" s="9" t="inlineStr">
+        <is>
+          <t>สทธ.69-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>วารีรัตน์ อังครุฑ</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>ฟิว</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>6932040028</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>student123</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>student</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>สทธ.69-11</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1809,7 @@
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -1790,7 +1930,7 @@
       </c>
       <c r="F4" s="11" t="inlineStr">
         <is>
-          <t>บัญชีทดสอบ / ทีม ปวีณา</t>
+          <t>บัญชีทดสอบ</t>
         </is>
       </c>
     </row>
@@ -1805,15 +1945,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="32" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -1844,7 +1984,7 @@
       </c>
       <c r="F1" s="12" t="inlineStr">
         <is>
-          <t>ทีม / หมายเหตุ</t>
+          <t>ห้อง / หมายเหตุ</t>
         </is>
       </c>
     </row>
@@ -1874,7 +2014,7 @@
       </c>
       <c r="F2" s="13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>ผู้ดูแลระบบหลัก</t>
         </is>
       </c>
     </row>
@@ -1934,7 +2074,7 @@
       </c>
       <c r="F4" s="13" t="inlineStr">
         <is>
-          <t>ทีม ปวีณา (นักเรียน 01-07)</t>
+          <t>ทีม ปวีณา</t>
         </is>
       </c>
     </row>
@@ -1964,7 +2104,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>ทีม กุลิสรา (นักเรียน 08-14)</t>
+          <t>ทีม กุลิสรา</t>
         </is>
       </c>
     </row>
@@ -1994,7 +2134,7 @@
       </c>
       <c r="F6" s="13" t="inlineStr">
         <is>
-          <t>ทีม อัญชลี (นักเรียน 15-20)</t>
+          <t>ทีม อัญชลี</t>
         </is>
       </c>
     </row>
@@ -2064,12 +2204,12 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>กฤติยาภรณ์ เพ็ชรดี</t>
+          <t>ศิริญา นาคสมบูรณ์</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>student01</t>
+          <t>6932040001</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
@@ -2084,7 +2224,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>ทีม ปวีณา</t>
+          <t>สทธ.69-11</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2234,12 @@
       </c>
       <c r="B10" s="13" t="inlineStr">
         <is>
-          <t>สุทธิตา แซ่ลิ้ม</t>
+          <t>ธนากร บัวติ๊บ</t>
         </is>
       </c>
       <c r="C10" s="13" t="inlineStr">
         <is>
-          <t>student02</t>
+          <t>6932040002</t>
         </is>
       </c>
       <c r="D10" s="13" t="inlineStr">
@@ -2114,7 +2254,7 @@
       </c>
       <c r="F10" s="13" t="inlineStr">
         <is>
-          <t>ทีม ปวีณา</t>
+          <t>สทธ.69-11</t>
         </is>
       </c>
     </row>
@@ -2124,12 +2264,12 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>เพ็ญพิชญา มีสรรเสริญ</t>
+          <t>ดานิโล อโนทัย เดนตี้</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>student03</t>
+          <t>6932040003</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
@@ -2144,7 +2284,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>ทีม ปวีณา</t>
+          <t>สทธ.69-11</t>
         </is>
       </c>
     </row>
@@ -2154,12 +2294,12 @@
       </c>
       <c r="B12" s="13" t="inlineStr">
         <is>
-          <t>ญาณวรรณ ดาบทอง</t>
+          <t>พิชญา ประทุมเพ็ชร</t>
         </is>
       </c>
       <c r="C12" s="13" t="inlineStr">
         <is>
-          <t>student04</t>
+          <t>6932040006</t>
         </is>
       </c>
       <c r="D12" s="13" t="inlineStr">
@@ -2174,7 +2314,7 @@
       </c>
       <c r="F12" s="13" t="inlineStr">
         <is>
-          <t>ทีม ปวีณา</t>
+          <t>สทธ.69-11</t>
         </is>
       </c>
     </row>
@@ -2184,12 +2324,12 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>จุติรัตน์ วังเวง</t>
+          <t>วันสุ นิ่มประเสริฐ</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>student05</t>
+          <t>6932040007</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
@@ -2204,7 +2344,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>ทีม ปวีณา</t>
+          <t>สทธ.69-11</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2354,12 @@
       </c>
       <c r="B14" s="13" t="inlineStr">
         <is>
-          <t>นิตินัดดา สายศรี</t>
+          <t>วรชิต เขียวหวาน</t>
         </is>
       </c>
       <c r="C14" s="13" t="inlineStr">
         <is>
-          <t>student06</t>
+          <t>6932040008</t>
         </is>
       </c>
       <c r="D14" s="13" t="inlineStr">
@@ -2234,7 +2374,7 @@
       </c>
       <c r="F14" s="13" t="inlineStr">
         <is>
-          <t>ทีม ปวีณา</t>
+          <t>สทธ.69-11</t>
         </is>
       </c>
     </row>
@@ -2244,12 +2384,12 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>ศิริวิมล อ่ำอิ่ม</t>
+          <t>ปวเรศ จำพานิชย์</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>student07</t>
+          <t>6932040009</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
@@ -2264,7 +2404,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>ทีม ปวีณา</t>
+          <t>สทธ.69-11</t>
         </is>
       </c>
     </row>
@@ -2274,12 +2414,12 @@
       </c>
       <c r="B16" s="13" t="inlineStr">
         <is>
-          <t>อภิชญา เมืองศิริ</t>
+          <t>เสฎฐวุฒิ แสนบุญมี</t>
         </is>
       </c>
       <c r="C16" s="13" t="inlineStr">
         <is>
-          <t>student08</t>
+          <t>6932040010</t>
         </is>
       </c>
       <c r="D16" s="13" t="inlineStr">
@@ -2294,7 +2434,7 @@
       </c>
       <c r="F16" s="13" t="inlineStr">
         <is>
-          <t>ทีม กุลิสรา</t>
+          <t>สทธ.69-11</t>
         </is>
       </c>
     </row>
@@ -2304,12 +2444,12 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>เมธนิยา ยางคำ</t>
+          <t>ปวีณ์นุช บินหะยีอาระซัน</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>student09</t>
+          <t>6932040011</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
@@ -2324,7 +2464,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>ทีม กุลิสรา</t>
+          <t>สทธ.69-11</t>
         </is>
       </c>
     </row>
@@ -2334,12 +2474,12 @@
       </c>
       <c r="B18" s="13" t="inlineStr">
         <is>
-          <t>ณัฐภัทร กอบสันเทียะ</t>
+          <t>ฟ่ะฮัด ชัยพฤกษ์</t>
         </is>
       </c>
       <c r="C18" s="13" t="inlineStr">
         <is>
-          <t>student10</t>
+          <t>6932040012</t>
         </is>
       </c>
       <c r="D18" s="13" t="inlineStr">
@@ -2354,7 +2494,7 @@
       </c>
       <c r="F18" s="13" t="inlineStr">
         <is>
-          <t>ทีม กุลิสรา</t>
+          <t>สทธ.69-11</t>
         </is>
       </c>
     </row>
@@ -2364,12 +2504,12 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>พรนภัส ภูฆัง</t>
+          <t>ปฏิวิทย์ แซ่ลิ่ม</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>student11</t>
+          <t>6932040013</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
@@ -2384,7 +2524,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>ทีม กุลิสรา</t>
+          <t>สทธ.69-11</t>
         </is>
       </c>
     </row>
@@ -2394,12 +2534,12 @@
       </c>
       <c r="B20" s="13" t="inlineStr">
         <is>
-          <t>กุลธิดา บุญเฮง</t>
+          <t>ถิระศักดิ์ ไสยกิจ</t>
         </is>
       </c>
       <c r="C20" s="13" t="inlineStr">
         <is>
-          <t>student12</t>
+          <t>6932040015</t>
         </is>
       </c>
       <c r="D20" s="13" t="inlineStr">
@@ -2414,7 +2554,7 @@
       </c>
       <c r="F20" s="13" t="inlineStr">
         <is>
-          <t>ทีม กุลิสรา</t>
+          <t>สทธ.69-11</t>
         </is>
       </c>
     </row>
@@ -2424,12 +2564,12 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>วัชรวิทย์ ดาราวงศ์</t>
+          <t>กนกวรรณ สุภาพ</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>student13</t>
+          <t>6932040016</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
@@ -2444,7 +2584,7 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>ทีม กุลิสรา</t>
+          <t>สทธ.69-11</t>
         </is>
       </c>
     </row>
@@ -2454,12 +2594,12 @@
       </c>
       <c r="B22" s="13" t="inlineStr">
         <is>
-          <t>หทัยกาญ ศิริถาวรเลิศสกุล</t>
+          <t>ประวีณ ผลถวิล</t>
         </is>
       </c>
       <c r="C22" s="13" t="inlineStr">
         <is>
-          <t>student14</t>
+          <t>6932040017</t>
         </is>
       </c>
       <c r="D22" s="13" t="inlineStr">
@@ -2474,7 +2614,7 @@
       </c>
       <c r="F22" s="13" t="inlineStr">
         <is>
-          <t>ทีม กุลิสรา</t>
+          <t>สทธ.69-11</t>
         </is>
       </c>
     </row>
@@ -2484,12 +2624,12 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>วิทวัส หลักเพชร</t>
+          <t>กัญญาวีร์ พิทักษ์ลักษณ์</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>student15</t>
+          <t>6932040018</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
@@ -2504,7 +2644,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>ทีม อัญชลี</t>
+          <t>สทธ.69-11</t>
         </is>
       </c>
     </row>
@@ -2514,12 +2654,12 @@
       </c>
       <c r="B24" s="13" t="inlineStr">
         <is>
-          <t>ศิริประภา เสภารัตน์</t>
+          <t>เคอหนุ่ม</t>
         </is>
       </c>
       <c r="C24" s="13" t="inlineStr">
         <is>
-          <t>student16</t>
+          <t>6932040020</t>
         </is>
       </c>
       <c r="D24" s="13" t="inlineStr">
@@ -2534,7 +2674,7 @@
       </c>
       <c r="F24" s="13" t="inlineStr">
         <is>
-          <t>ทีม อัญชลี</t>
+          <t>สทธ.69-11</t>
         </is>
       </c>
     </row>
@@ -2544,12 +2684,12 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>วิภาช บรรจงอักษร</t>
+          <t>ทิราภรณ์ ทองเกษมศรี</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>student17</t>
+          <t>6932040021</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
@@ -2564,7 +2704,7 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>ทีม อัญชลี</t>
+          <t>สทธ.69-11</t>
         </is>
       </c>
     </row>
@@ -2574,12 +2714,12 @@
       </c>
       <c r="B26" s="13" t="inlineStr">
         <is>
-          <t>ขจรเกียรติ สุขบัติ</t>
+          <t>ธนัชชา จุ้ยรอด</t>
         </is>
       </c>
       <c r="C26" s="13" t="inlineStr">
         <is>
-          <t>student18</t>
+          <t>6932040022</t>
         </is>
       </c>
       <c r="D26" s="13" t="inlineStr">
@@ -2594,7 +2734,7 @@
       </c>
       <c r="F26" s="13" t="inlineStr">
         <is>
-          <t>ทีม อัญชลี</t>
+          <t>สทธ.69-11</t>
         </is>
       </c>
     </row>
@@ -2604,12 +2744,12 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>จักรพรรดิ์ อาวาส</t>
+          <t>สุภัสสรา บุญแต่ง</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>student19</t>
+          <t>6932040023</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
@@ -2624,7 +2764,7 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>ทีม อัญชลี</t>
+          <t>สทธ.69-11</t>
         </is>
       </c>
     </row>
@@ -2634,12 +2774,12 @@
       </c>
       <c r="B28" s="13" t="inlineStr">
         <is>
-          <t>อดิเทพ พลทะสี</t>
+          <t>ธัญกมล เพ็ชรธนดำรง</t>
         </is>
       </c>
       <c r="C28" s="13" t="inlineStr">
         <is>
-          <t>student20</t>
+          <t>6932040024</t>
         </is>
       </c>
       <c r="D28" s="13" t="inlineStr">
@@ -2654,7 +2794,7 @@
       </c>
       <c r="F28" s="13" t="inlineStr">
         <is>
-          <t>ทีม อัญชลี</t>
+          <t>สทธ.69-11</t>
         </is>
       </c>
     </row>
@@ -2664,27 +2804,27 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>ครู ทดสอบ</t>
+          <t>สุจิรา วงศ์เกิดสุข</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>teacher_test</t>
+          <t>6932040025</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>teacher123</t>
+          <t>student123</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>teacher</t>
+          <t>student</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>บัญชีทดสอบ</t>
+          <t>สทธ.69-11</t>
         </is>
       </c>
     </row>
@@ -2694,27 +2834,27 @@
       </c>
       <c r="B30" s="13" t="inlineStr">
         <is>
-          <t>ปราชญ์ ทดสอบ</t>
+          <t>ตรีรัตน์ ศรีภุมมา</t>
         </is>
       </c>
       <c r="C30" s="13" t="inlineStr">
         <is>
-          <t>sage_test</t>
+          <t>6932040026</t>
         </is>
       </c>
       <c r="D30" s="13" t="inlineStr">
         <is>
-          <t>sage123</t>
+          <t>student123</t>
         </is>
       </c>
       <c r="E30" s="13" t="inlineStr">
         <is>
-          <t>sage</t>
+          <t>student</t>
         </is>
       </c>
       <c r="F30" s="13" t="inlineStr">
         <is>
-          <t>บัญชีทดสอบ</t>
+          <t>สทธ.69-11</t>
         </is>
       </c>
     </row>
@@ -2724,27 +2864,147 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
+          <t>วัชรวิศว์ เปล่งปลั่ง</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>6932040027</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>student123</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>student</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>สทธ.69-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="13" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="13" t="inlineStr">
+        <is>
+          <t>วารีรัตน์ อังครุฑ</t>
+        </is>
+      </c>
+      <c r="C32" s="13" t="inlineStr">
+        <is>
+          <t>6932040028</t>
+        </is>
+      </c>
+      <c r="D32" s="13" t="inlineStr">
+        <is>
+          <t>student123</t>
+        </is>
+      </c>
+      <c r="E32" s="13" t="inlineStr">
+        <is>
+          <t>student</t>
+        </is>
+      </c>
+      <c r="F32" s="13" t="inlineStr">
+        <is>
+          <t>สทธ.69-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="5" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>ครู ทดสอบ</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>teacher_test</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>teacher123</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>teacher</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t>บัญชีทดสอบ</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="13" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="13" t="inlineStr">
+        <is>
+          <t>ปราชญ์ ทดสอบ</t>
+        </is>
+      </c>
+      <c r="C34" s="13" t="inlineStr">
+        <is>
+          <t>sage_test</t>
+        </is>
+      </c>
+      <c r="D34" s="13" t="inlineStr">
+        <is>
+          <t>sage123</t>
+        </is>
+      </c>
+      <c r="E34" s="13" t="inlineStr">
+        <is>
+          <t>sage</t>
+        </is>
+      </c>
+      <c r="F34" s="13" t="inlineStr">
+        <is>
+          <t>บัญชีทดสอบ</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="5" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
           <t>นักเรียน ทดสอบ</t>
         </is>
       </c>
-      <c r="C31" s="5" t="inlineStr">
+      <c r="C35" s="5" t="inlineStr">
         <is>
           <t>student_test</t>
         </is>
       </c>
-      <c r="D31" s="5" t="inlineStr">
-        <is>
-          <t>student123</t>
-        </is>
-      </c>
-      <c r="E31" s="5" t="inlineStr">
-        <is>
-          <t>student</t>
-        </is>
-      </c>
-      <c r="F31" s="5" t="inlineStr">
-        <is>
-          <t>บัญชีทดสอบ / ทีม ปวีณา</t>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>student123</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>student</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>บัญชีทดสอบ</t>
         </is>
       </c>
     </row>

--- a/r-eco-pilot_users.xlsx
+++ b/r-eco-pilot_users.xlsx
@@ -9,10 +9,11 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Admin" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Teachers" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sages" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="นักศึกษา สทธ.69-11" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Accounts" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ทั้งหมด" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="อาจารย์ (ชุดใหม่)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sages" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="นักศึกษา สทธ.69-11" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Accounts" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ทั้งหมด" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,7 +23,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -40,8 +41,13 @@
       <name val="Arial"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="14">
+  <fills count="16">
     <fill>
       <patternFill/>
     </fill>
@@ -108,8 +114,20 @@
         <fgColor rgb="00ECEFF1"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001E3A5F"/>
+        <bgColor rgb="001E3A5F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EBF5FB"/>
+        <bgColor rgb="00EBF5FB"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -131,11 +149,25 @@
         <color rgb="00BDBDBD"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BDC3C7"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BDC3C7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BDC3C7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BDC3C7"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -175,6 +207,21 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -799,6 +846,300 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="14" t="inlineStr">
+        <is>
+          <t>ลำดับ</t>
+        </is>
+      </c>
+      <c r="B1" s="14" t="inlineStr">
+        <is>
+          <t>ชื่อ-นามสกุล (ไทย)</t>
+        </is>
+      </c>
+      <c r="C1" s="14" t="inlineStr">
+        <is>
+          <t>ชื่อ (English)</t>
+        </is>
+      </c>
+      <c r="D1" s="14" t="inlineStr">
+        <is>
+          <t>Username</t>
+        </is>
+      </c>
+      <c r="E1" s="14" t="inlineStr">
+        <is>
+          <t>Password</t>
+        </is>
+      </c>
+      <c r="F1" s="14" t="inlineStr">
+        <is>
+          <t>Role</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="16" t="inlineStr">
+        <is>
+          <t>อาจารย์ณัฏฐนันท์ นวลประสิทธิ์กุล</t>
+        </is>
+      </c>
+      <c r="C2" s="16" t="inlineStr">
+        <is>
+          <t>Miss Nattanan Nuanprasitkun</t>
+        </is>
+      </c>
+      <c r="D2" s="16" t="inlineStr">
+        <is>
+          <t>nattanan</t>
+        </is>
+      </c>
+      <c r="E2" s="16" t="inlineStr">
+        <is>
+          <t>teacher123</t>
+        </is>
+      </c>
+      <c r="F2" s="16" t="inlineStr">
+        <is>
+          <t>teacher</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="18" t="inlineStr">
+        <is>
+          <t>อาจารย์กฤษฎา ทองกำเหนิด</t>
+        </is>
+      </c>
+      <c r="C3" s="18" t="inlineStr">
+        <is>
+          <t>Miss Kritsada Thongkamnerd</t>
+        </is>
+      </c>
+      <c r="D3" s="18" t="inlineStr">
+        <is>
+          <t>kritsada</t>
+        </is>
+      </c>
+      <c r="E3" s="18" t="inlineStr">
+        <is>
+          <t>teacher123</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>teacher</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="16" t="inlineStr">
+        <is>
+          <t>อาจารย์ฐิติรัตน์ ชาติไทยเจริญ</t>
+        </is>
+      </c>
+      <c r="C4" s="16" t="inlineStr">
+        <is>
+          <t>Miss Thitirat Chatthaicharoen</t>
+        </is>
+      </c>
+      <c r="D4" s="16" t="inlineStr">
+        <is>
+          <t>thitirat</t>
+        </is>
+      </c>
+      <c r="E4" s="16" t="inlineStr">
+        <is>
+          <t>teacher123</t>
+        </is>
+      </c>
+      <c r="F4" s="16" t="inlineStr">
+        <is>
+          <t>teacher</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="18" t="inlineStr">
+        <is>
+          <t>อาจารย์เจนจบ มาเพ็ชร์</t>
+        </is>
+      </c>
+      <c r="C5" s="18" t="inlineStr">
+        <is>
+          <t>Mr. Chenjop Mapech</t>
+        </is>
+      </c>
+      <c r="D5" s="18" t="inlineStr">
+        <is>
+          <t>chenjop</t>
+        </is>
+      </c>
+      <c r="E5" s="18" t="inlineStr">
+        <is>
+          <t>teacher123</t>
+        </is>
+      </c>
+      <c r="F5" s="18" t="inlineStr">
+        <is>
+          <t>teacher</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="16" t="inlineStr">
+        <is>
+          <t>อาจารย์สุธาทิพย์ พลตรี</t>
+        </is>
+      </c>
+      <c r="C6" s="16" t="inlineStr">
+        <is>
+          <t>Miss Suthathip Poltree</t>
+        </is>
+      </c>
+      <c r="D6" s="16" t="inlineStr">
+        <is>
+          <t>suthathip</t>
+        </is>
+      </c>
+      <c r="E6" s="16" t="inlineStr">
+        <is>
+          <t>teacher123</t>
+        </is>
+      </c>
+      <c r="F6" s="16" t="inlineStr">
+        <is>
+          <t>teacher</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="18" t="inlineStr">
+        <is>
+          <t>อาจารย์บรรพต นิลพาณิชย์</t>
+        </is>
+      </c>
+      <c r="C7" s="18" t="inlineStr">
+        <is>
+          <t>Mr. Banphot Ninpanit</t>
+        </is>
+      </c>
+      <c r="D7" s="18" t="inlineStr">
+        <is>
+          <t>banphot</t>
+        </is>
+      </c>
+      <c r="E7" s="18" t="inlineStr">
+        <is>
+          <t>teacher123</t>
+        </is>
+      </c>
+      <c r="F7" s="18" t="inlineStr">
+        <is>
+          <t>teacher</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="16" t="inlineStr">
+        <is>
+          <t>อาจารย์วิไลวรรณ นวลละออง</t>
+        </is>
+      </c>
+      <c r="C8" s="16" t="inlineStr">
+        <is>
+          <t>Miss Wilaiwan Nuanla-ong</t>
+        </is>
+      </c>
+      <c r="D8" s="16" t="inlineStr">
+        <is>
+          <t>wilaiwan</t>
+        </is>
+      </c>
+      <c r="E8" s="16" t="inlineStr">
+        <is>
+          <t>teacher123</t>
+        </is>
+      </c>
+      <c r="F8" s="16" t="inlineStr">
+        <is>
+          <t>teacher</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="18" t="inlineStr">
+        <is>
+          <t>อาจารย์สุมาลี ยืนยงนาวิน</t>
+        </is>
+      </c>
+      <c r="C9" s="18" t="inlineStr">
+        <is>
+          <t>Miss Sumalee Yuenyongnawin</t>
+        </is>
+      </c>
+      <c r="D9" s="18" t="inlineStr">
+        <is>
+          <t>sumalee</t>
+        </is>
+      </c>
+      <c r="E9" s="18" t="inlineStr">
+        <is>
+          <t>teacher123</t>
+        </is>
+      </c>
+      <c r="F9" s="18" t="inlineStr">
+        <is>
+          <t>teacher</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -907,7 +1248,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1795,7 +2136,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1939,13 +2280,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -3008,6 +3349,230 @@
         </is>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>อาจารย์ชุดใหม่ #1</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>อาจารย์ณัฏฐนันท์ นวลประสิทธิ์กุล</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>nattanan</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>teacher123</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>teacher</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>อาจารย์ชุดใหม่ #2</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>อาจารย์กฤษฎา ทองกำเหนิด</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>kritsada</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>teacher123</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>teacher</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>อาจารย์ชุดใหม่ #3</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>อาจารย์ฐิติรัตน์ ชาติไทยเจริญ</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>thitirat</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>teacher123</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>teacher</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>อาจารย์ชุดใหม่ #4</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>อาจารย์เจนจบ มาเพ็ชร์</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>chenjop</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>teacher123</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>teacher</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>อาจารย์ชุดใหม่ #5</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>อาจารย์สุธาทิพย์ พลตรี</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>suthathip</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>teacher123</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>teacher</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>อาจารย์ชุดใหม่ #6</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>อาจารย์บรรพต นิลพาณิชย์</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>banphot</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>teacher123</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>teacher</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>อาจารย์ชุดใหม่ #7</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>อาจารย์วิไลวรรณ นวลละออง</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>wilaiwan</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>teacher123</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>teacher</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>อาจารย์ชุดใหม่ #8</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>อาจารย์สุมาลี ยืนยงนาวิน</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>sumalee</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>teacher123</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>teacher</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
